--- a/Extracted_data_analysis/polar/Output-Transformed_data/Realm_count.xlsx
+++ b/Extracted_data_analysis/polar/Output-Transformed_data/Realm_count.xlsx
@@ -381,7 +381,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
